--- a/excel-files/LAS PINAS/LAS PIÑAS CITY NATIONAL SCIENCE HIGH SCHOOL.xlsx
+++ b/excel-files/LAS PINAS/LAS PIÑAS CITY NATIONAL SCIENCE HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="304" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5750C4B-6525-4962-B517-651EE9D05BB9}"/>
+  <xr:revisionPtr revIDLastSave="467" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0438DCFD-8ED2-40B3-934D-FB47943E36AB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5676,7 +5676,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5901,7 +5901,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="38.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5970,7 +5970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -6039,7 +6039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -6108,7 +6108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -6177,7 +6177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6315,7 +6315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" ht="19.5">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6384,7 +6384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="19.5">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6535,7 +6535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6604,7 +6604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6673,7 +6673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6742,7 +6742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6880,7 +6880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" ht="19.5">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6949,7 +6949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="19.5">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -7101,7 +7101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -7170,7 +7170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7239,7 +7239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7308,7 +7308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7377,7 +7377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7446,7 +7446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" ht="19.5">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7584,7 +7584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7736,7 +7736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7805,7 +7805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="19.5">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7874,7 +7874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7943,7 +7943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="38.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -8012,7 +8012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -8081,7 +8081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -8150,7 +8150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8219,7 +8219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8288,7 +8288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8302,7 +8302,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8371,7 +8371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8440,7 +8440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8509,7 +8509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8578,7 +8578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8647,7 +8647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8716,7 +8716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8785,7 +8785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8854,7 +8854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -9006,7 +9006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" ht="19.5">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -9075,7 +9075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -9144,7 +9144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9213,7 +9213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="38.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9282,7 +9282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9351,7 +9351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="19.5">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9489,7 +9489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="K83" s="12"/>
       <c r="L83" s="10"/>
-      <c r="M83" s="12"/>
+      <c r="M83" s="10"/>
       <c r="N83" s="12">
         <f t="shared" si="16"/>
         <v>960</v>
@@ -12454,7 +12454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="1" t="s">
         <v>25</v>
       </c>
@@ -12523,7 +12523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="38.25">
       <c r="A107" s="1" t="s">
         <v>25</v>
       </c>
@@ -12630,9 +12630,7 @@
       <c r="K108" s="5">
         <v>148</v>
       </c>
-      <c r="L108" s="1">
-        <v>2025</v>
-      </c>
+      <c r="L108" s="1"/>
       <c r="M108" s="5" t="s">
         <v>65</v>
       </c>
@@ -12744,7 +12742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="38.25">
       <c r="A110" s="1" t="s">
         <v>25</v>
       </c>
@@ -12886,7 +12884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="19.5">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12948,7 +12946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="19.5">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -13010,7 +13008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="19.5">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -13072,7 +13070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="19.5">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -13134,7 +13132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="19.5">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -13196,7 +13194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="19.5">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -13258,7 +13256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="19.5">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -13320,7 +13318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="19.5">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13382,7 +13380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="19.5">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13444,7 +13442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="19.5">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13506,7 +13504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="19.5">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13568,7 +13566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="19.5">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13630,7 +13628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="19.5">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13692,7 +13690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="19.5">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13754,7 +13752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="19.5">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13775,7 +13773,7 @@
         <v>0</v>
       </c>
       <c r="K127" s="31"/>
-      <c r="L127" s="29"/>
+      <c r="L127" s="1"/>
       <c r="M127" s="31"/>
       <c r="N127" s="5">
         <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
@@ -13787,7 +13785,7 @@
       </c>
       <c r="P127" s="5"/>
       <c r="Q127" s="31"/>
-      <c r="R127" s="29"/>
+      <c r="R127" s="1"/>
       <c r="S127" s="31"/>
       <c r="T127" s="5">
         <f t="shared" si="18"/>
@@ -13802,7 +13800,7 @@
         <v>0</v>
       </c>
       <c r="W127" s="31"/>
-      <c r="X127" s="29"/>
+      <c r="X127" s="1"/>
       <c r="Y127" s="31"/>
       <c r="Z127" s="5">
         <f t="shared" si="20"/>
@@ -13813,191 +13811,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C103:C110 C112:C127 C5:C12 C63:C71 C73:C81 C83:C91 C93:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D83:F91" name="LAS"/>
-    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 D23:F31 D33:F41 H33:I41 D43:F51 H43:I51 D53:F61 H53:I61 D63:F71 H63:I71 D73:F81 H73:I81 H83:I91 D93:F101 H93:I101 D103:F110 H103:I110 D112:F127 H112:I127 N127:Q127 H14:I21 H23:I31 H6:I12 Q112:R112 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D83:F91 K6:L12 K14:L21 K23:L31 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 M83 K83:L91 K93:L101 K103:L110 K112:L127 N5:R12 Q14:R21 Q23:R31 Q33:R41 Q43:R51 Q53:R61 Q63:R71 Q73:R81 Q83:R91 Q93:R101 Q103:R110 Q113:Q126 R113:R127 T5:X12 W14:X21 W23:X31 W33:X41 W43:X51 W53:X61 W63:X71 W73:X81 W83:X91 W93:X101 W103:X110 W112:X127" name="LAS"/>
+    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M82 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110 M84:M110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -14006,15 +13824,21 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F33:F41 F103:F110 F93:F101 M83 F43:F51 F5:F12 F73:F81 F14:F21 F83:F91 F23:F31 F63:F71 F53:F61 F112:F127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G103:G110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 M14:M82 M84:M110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L107 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110 X112:X127" xr:uid="{3D5505A5-EA0A-4C3D-8692-C56E0F9AE0EF}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L108:L110" xr:uid="{6644EFE9-E1C4-4F55-AFE3-9E6306D41D21}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14029,7 +13853,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -14244,7 +14068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999">
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -14313,7 +14137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="19.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -14382,7 +14206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14451,7 +14275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14520,7 +14344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14589,7 +14413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14658,7 +14482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14797,7 +14621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999">
+    <row r="13" spans="1:27" ht="19.5">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14866,7 +14690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="19.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14935,7 +14759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -15004,7 +14828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -15073,7 +14897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -15142,7 +14966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -15211,7 +15035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -15350,7 +15174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999">
+    <row r="22" spans="1:27" ht="19.5">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15419,7 +15243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="19.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15488,7 +15312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15557,7 +15381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15626,7 +15450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15695,7 +15519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15764,7 +15588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15833,7 +15657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15972,7 +15796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999">
+    <row r="32" spans="1:27" ht="19.5">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -16041,7 +15865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -16110,7 +15934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -16179,7 +16003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="38.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -16248,7 +16072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -16317,7 +16141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="19.5">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -16386,7 +16210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16455,7 +16279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16524,7 +16348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16593,7 +16417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16732,7 +16556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16801,7 +16625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16870,7 +16694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16939,7 +16763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -17008,7 +16832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -17077,7 +16901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -17146,7 +16970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -17215,7 +17039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -17284,7 +17108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999">
+    <row r="52" spans="1:27" ht="19.5">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -17353,7 +17177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -17492,7 +17316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17561,7 +17385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="19.5">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17630,7 +17454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17699,7 +17523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="38.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17768,7 +17592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17837,7 +17661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17906,7 +17730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999">
+    <row r="62" spans="1:27" ht="19.5">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17975,7 +17799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -18044,7 +17868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -18113,7 +17937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -21432,7 +21256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="19.5">
       <c r="A116" s="1" t="s">
         <v>25</v>
       </c>
@@ -21501,7 +21325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="19.5">
       <c r="A117" s="1" t="s">
         <v>25</v>
       </c>
@@ -21570,7 +21394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="19.5">
       <c r="A118" s="1" t="s">
         <v>25</v>
       </c>
@@ -21639,7 +21463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="38.25">
       <c r="A119" s="1" t="s">
         <v>25</v>
       </c>
@@ -21708,7 +21532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="38.25">
       <c r="A120" s="1" t="s">
         <v>25</v>
       </c>
@@ -21777,7 +21601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="57.75">
       <c r="A121" s="1" t="s">
         <v>25</v>
       </c>
@@ -21846,7 +21670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>25</v>
       </c>
@@ -22426,190 +22250,10 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C115:C122 C91:C101 C103:C113 C67:C77 C79:C89" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D94:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113 D91:D93 F91:F93" name="LAS"/>
+    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D94:F101 D115:F122 N3:O10 T3:U10 Z3:AA10 Z12:AA19 Z21:AA29 Z31:AA41 Z43:AA53 Z55:AA65 Z67:AA77 Z79:AA89 Z91:AA101 Z103:AA113 Z115:AA122 D103:F113 D91:D93 F91:F93 H3:L10 H12:L19 H21:L29 H31:L41 H43:L53 H55:L65 H67:L77 H79:L89 H91:L101 H103:L113 H115:L122 P2:R10 N12:R19 N21:R29 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113 N115:R122 V2:X10 T12:X19 T21:X29 T31:X41 T43:X53 T55:X65 T67:X77 T79:X89 T91:X101 T103:X113 T115:X122" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
     <protectedRange sqref="E91:E93" name="LAS_1"/>
   </protectedRanges>
@@ -22620,12 +22264,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F103:F113 F67:F77 F79:F89 F115:F122 F3:F10 F55:F65 F91:F101 F12:F19 F21:F29 F43:F53 F31:F41" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113 X115:X116 X117:X122" xr:uid="{DB141B39-98E3-4983-B12C-D7FDF73D0865}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
